--- a/artfynd/A 41657-2025 artfynd.xlsx
+++ b/artfynd/A 41657-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129147730</v>
       </c>
       <c r="B2" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129147729</v>
       </c>
       <c r="B3" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129147731</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41657-2025 artfynd.xlsx
+++ b/artfynd/A 41657-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129147730</v>
       </c>
       <c r="B2" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129147729</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129147731</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41657-2025 artfynd.xlsx
+++ b/artfynd/A 41657-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129147730</v>
       </c>
       <c r="B2" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129147729</v>
       </c>
       <c r="B3" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129147731</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41657-2025 artfynd.xlsx
+++ b/artfynd/A 41657-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129147730</v>
       </c>
       <c r="B2" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129147729</v>
       </c>
       <c r="B3" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129147731</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41657-2025 artfynd.xlsx
+++ b/artfynd/A 41657-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129147730</v>
       </c>
       <c r="B2" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129147729</v>
       </c>
       <c r="B3" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129147731</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41657-2025 artfynd.xlsx
+++ b/artfynd/A 41657-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129147730</v>
       </c>
       <c r="B2" t="n">
-        <v>80184</v>
+        <v>80210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129147729</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129147731</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
